--- a/Databases/Database3/Output/2015/db3_2015_with_ids.xlsx
+++ b/Databases/Database3/Output/2015/db3_2015_with_ids.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>UL:S; UR:FW; LR:OB</t>
+          <t>UL:S; LL:-; UR:FW; LR:OB</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>UL:FG; LL:BO; LR:WB</t>
+          <t>UL:FG; LL:BO; UR:-; LR:WB</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -759,7 +759,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>UL:O; LL:O/Y; UR:S</t>
+          <t>UL:O; LL:O/Y; UR:S; LR:-</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1035,7 +1035,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>UL:O; LL:Lb; UR:S</t>
+          <t>UL:O; LL:Lb; UR:S; LR:-</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9:17-10:57</t>
+          <t>09:17 - 10:57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8:12 - 10:12</t>
+          <t>08:12 - 10:12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8:12 - 10:12</t>
+          <t>08:12 - 10:12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8:12 - 10:12</t>
+          <t>08:12 - 10:12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9:00-11:45am</t>
+          <t>09:00 - 11:45</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1606,7 +1606,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>LR:A/B</t>
+          <t>UL:-; LL:-; UR:-; LR:A/B</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0900-1115</t>
+          <t>09:00 - 11:15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0900-1115</t>
+          <t>09:00 - 11:15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>07:30-14:30 EST</t>
+          <t>07:30 - 14:30</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>07:30-14:30 EST</t>
+          <t>07:30 - 14:30</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>LL:G; UR:FG; LR:GK</t>
+          <t>UL:-; LL:G; UR:FG; LR:GK</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>07:30-14:30 EST</t>
+          <t>07:30 - 14:30</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>UL:FG; LL:BB; LR:Y</t>
+          <t>UL:FG; LL:BB; UR:-; LR:Y</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>LL:YO; UR:FG; LR:WY</t>
+          <t>UL:-; LL:YO; UR:FG; LR:WY</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>UL:FY; UR:S</t>
+          <t>UL:FY; LL:-; UR:S; LR:-</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1130-1230</t>
+          <t>11:30 - 12:30</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1130-1230</t>
+          <t>11:30 - 12:30</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>12:34-2;45</t>
+          <t>12:34 - 02:45</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>11:00-3:30</t>
+          <t>11:00 - 03:30</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>11:00-3:30</t>
+          <t>11:00 - 03:30</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>11:00-3:30</t>
+          <t>11:00 - 03:30</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3249,7 +3249,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>UL:O; UR:S; LR:Lg/O/Lg</t>
+          <t>UL:O; LL:-; UR:S; LR:Lg/O/Lg</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>UL:FG; LL:BK; LR:GY</t>
+          <t>UL:FG; LL:BK; UR:-; LR:GY</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>UL:G; LL:KK; UR:FG</t>
+          <t>UL:G; LL:KK; UR:FG; LR:-</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>UL:FG; LL:YB; LR:WR</t>
+          <t>UL:FG; LL:YB; UR:-; LR:WR</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:Yf; UR:S</t>
+          <t>Orientation:Horizontal; UL:Yf; LL:-; UR:S; LR:-</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>UL:Gf; LL:OO; LR:WB</t>
+          <t>UL:Gf; LL:OO; UR:-; LR:WB</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>UL:Of; LL:RR; LR:bS</t>
+          <t>UL:Of; LL:RR; UR:-; LR:bS</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>8:20-10:20 am</t>
+          <t>08:20 - 10:20</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4448,7 +4448,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>UL:R; LL:G/B; LR:Y/G/R</t>
+          <t>UL:R; LL:G/B; UR:-; LR:Y/G/R</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>8:20-10:20 am</t>
+          <t>08:20 - 10:20</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9:40 am - 12:10 pm</t>
+          <t>09:40 - 12:10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>7:30 - 9:00 am</t>
+          <t>07:30 - 09:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1245-1430</t>
+          <t>12:45 - 14:30</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1245-1430</t>
+          <t>12:45 - 14:30</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4893,7 +4893,11 @@
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
           <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -4924,7 +4928,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4962,7 +4966,11 @@
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
           <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -4993,7 +5001,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5031,7 +5039,11 @@
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5062,7 +5074,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5127,7 +5139,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5165,7 +5177,11 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
           <t>2 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5196,7 +5212,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5234,7 +5250,11 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
           <t>2 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5265,7 +5285,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5330,7 +5350,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5368,7 +5388,11 @@
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5399,7 +5423,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5437,7 +5461,11 @@
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr">
         <is>
           <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5468,7 +5496,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5506,7 +5534,11 @@
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5537,7 +5569,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5575,7 +5607,11 @@
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr">
         <is>
           <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5606,7 +5642,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5671,7 +5707,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>8:45-10:45</t>
+          <t>08:45 - 10:45</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5742,7 +5778,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>8:45-10:45</t>
+          <t>08:45 - 10:45</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5805,7 +5841,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5880,7 +5916,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5953,7 +5989,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6024,7 +6060,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6087,7 +6123,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6146,7 +6182,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6205,7 +6241,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6247,7 +6283,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>UL:S; LL:Lb or Lg; LR:0</t>
+          <t>UL:S; LL:Lb or Lg; UR:-; LR:0</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6280,7 +6316,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6339,7 +6375,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6398,7 +6434,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6461,7 +6497,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6524,7 +6560,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6583,7 +6619,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6625,7 +6661,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>UL:F(G); LL:B/B; LR:Y/W</t>
+          <t>UL:F(G); LL:B/B; UR:-; LR:Y/W</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6658,7 +6694,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6700,7 +6736,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>UL:F(G); LL:K; UR:G</t>
+          <t>UL:F(G); LL:K; UR:G; LR:-</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -6733,7 +6769,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6796,7 +6832,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6838,7 +6874,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Orientation:horizontal; UL:S; UR:F(A)</t>
+          <t>Orientation:horizontal; UL:S; LL:-; UR:F(A); LR:-</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -6867,7 +6903,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6926,7 +6962,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>09:12-10:35</t>
+          <t>09:12 - 10:35</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6989,7 +7025,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -7064,7 +7100,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -7106,7 +7142,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>UL:F(W); UR:S</t>
+          <t>UL:F(W); LL:-; UR:S; LR:-</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7139,7 +7175,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -7181,7 +7217,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>UL:F(G); LL:W/O; UR:Y</t>
+          <t>UL:F(G); LL:W/O; UR:Y; LR:-</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7214,7 +7250,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -7256,7 +7292,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>LL:W/W; UR:F(G); LR:O/Y</t>
+          <t>UL:-; LL:W/W; UR:F(G); LR:O/Y</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7289,7 +7325,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7364,7 +7400,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7427,7 +7463,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -7490,7 +7526,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>10:30 AM-12:30 PM</t>
+          <t>10:30 - 12:30</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7549,7 +7585,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -7620,7 +7656,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7691,7 +7727,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7754,7 +7790,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7817,7 +7853,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7922,7 +7958,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:FY; UR:S</t>
+          <t>Orientation:Horizontal; UL:FY; LL:-; UR:S; LR:-</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8068,7 +8104,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>UL:FG; LL:BG; LR:WB</t>
+          <t>UL:FG; LL:BG; UR:-; LR:WB</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8143,7 +8179,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:FY; LL:GB; LR:GP</t>
+          <t>Orientation:Horizontal; UL:FY; LL:GB; UR:-; LR:GP</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8663,7 +8699,7 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>UL:S; LL:BO</t>
+          <t>UL:S; LL:BO; UR:-; LR:-</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -8893,7 +8929,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>07:45 / 17:30</t>
+          <t>07:45 - 17:30</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8956,7 +8992,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>11:44-1:21</t>
+          <t>11:44 - 01:21</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -9015,7 +9051,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>11:44-1:21</t>
+          <t>11:44 - 01:21</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
